--- a/output/pdf_financials_xlsx/AGI.xlsx
+++ b/output/pdf_financials_xlsx/AGI.xlsx
@@ -5850,10 +5850,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-10.6</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-16.5</v>
       </c>
     </row>
     <row r="125">
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-10.6</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-16.5</v>
       </c>
     </row>
     <row r="126">
@@ -15181,7 +15181,11 @@
           <t>Lease payments (Note 16)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -16388,7 +16392,11 @@
           <t>Lease payments (Note 15)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
